--- a/Unity/Assets/Config/Excel/StoryChapterConfig.xlsx
+++ b/Unity/Assets/Config/Excel/StoryChapterConfig.xlsx
@@ -43,7 +43,7 @@
     <t>Name</t>
   </si>
   <si>
-    <t>Choice</t>
+    <t>Stories</t>
   </si>
   <si>
     <t>EntryTaskId</t>
@@ -11275,7 +11275,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2">
-    <tableStyle name="MySqlDefault" count="2" xr9:uid="{7CC98921-26D6-45B1-A7AB-5D7A9545FC79}">
+    <tableStyle name="MySqlDefault" count="2" xr9:uid="{7B9CF112-EB73-43DC-BBD1-632932B4A4C9}">
       <tableStyleElement type="wholeTable" dxfId="1"/>
       <tableStyleElement type="headerRow" dxfId="0"/>
     </tableStyle>

--- a/Unity/Assets/Config/Excel/StoryChapterConfig.xlsx
+++ b/Unity/Assets/Config/Excel/StoryChapterConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
   <si>
     <t>##var</t>
   </si>
@@ -86,6 +86,12 @@
   </si>
   <si>
     <t>1001,1002</t>
+  </si>
+  <si>
+    <t>第二章 归途</t>
+  </si>
+  <si>
+    <t>2001,2002</t>
   </si>
 </sst>
 </file>
@@ -11275,7 +11281,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2">
-    <tableStyle name="MySqlDefault" count="2" xr9:uid="{7B9CF112-EB73-43DC-BBD1-632932B4A4C9}">
+    <tableStyle name="MySqlDefault" count="2" xr9:uid="{FD64A4EA-D0C4-4FD3-B5E2-AD7FA1011AF7}">
       <tableStyleElement type="wholeTable" dxfId="1"/>
       <tableStyleElement type="headerRow" dxfId="0"/>
     </tableStyle>
@@ -11575,8 +11581,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="4"/>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="4"/>
   <cols>
     <col min="2" max="2" width="17.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="22" style="3" customWidth="1"/>
@@ -11660,6 +11666,20 @@
         <v>100001</v>
       </c>
     </row>
+    <row r="6" spans="1:5">
+      <c r="B6" s="2">
+        <v>1002</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="3">
+        <v>100002</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
